--- a/www/tematicas.xlsx
+++ b/www/tematicas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CLIENTE2\Downloads\SERVICIO SOCIAL - SESNA\Bundle Nuevo Leon - copia\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84078487-44E5-4977-B7B1-C5E1D2E99FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F01D7A-0577-465E-AFA9-9E910B698E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="17730" windowHeight="9945" xr2:uid="{784F576F-CCD7-4DA7-9E61-2F35978AD8B9}"/>
   </bookViews>
@@ -419,7 +419,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -434,40 +434,43 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A11">
+    <sortCondition ref="A2:A11"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>